--- a/artfynd/A 23506-2025 artfynd.xlsx
+++ b/artfynd/A 23506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111785255</v>
+        <v>111785288</v>
       </c>
       <c r="B2" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570786</v>
+        <v>570465</v>
       </c>
       <c r="R2" t="n">
-        <v>6962212</v>
+        <v>6962353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111785282</v>
+        <v>111785293</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570621</v>
+        <v>570512</v>
       </c>
       <c r="R3" t="n">
-        <v>6962391</v>
+        <v>6962472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111785276</v>
+        <v>111785289</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570639</v>
+        <v>570490</v>
       </c>
       <c r="R4" t="n">
-        <v>6962382</v>
+        <v>6962361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111785258</v>
+        <v>111785290</v>
       </c>
       <c r="B5" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570692</v>
+        <v>570657</v>
       </c>
       <c r="R5" t="n">
-        <v>6962273</v>
+        <v>6962473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111785288</v>
+        <v>111785291</v>
       </c>
       <c r="B6" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570465</v>
+        <v>570533</v>
       </c>
       <c r="R6" t="n">
-        <v>6962353</v>
+        <v>6962474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111785267</v>
+        <v>111785294</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>5321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Stensjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570490</v>
+        <v>570698</v>
       </c>
       <c r="R7" t="n">
-        <v>6962361</v>
+        <v>6962176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1242,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,16 +1264,11 @@
         <v>111785287</v>
       </c>
       <c r="B8" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570541</v>
+        <v>570542</v>
       </c>
       <c r="R8" t="n">
-        <v>6962349</v>
+        <v>6962350</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111785291</v>
+        <v>111785254</v>
       </c>
       <c r="B9" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570532</v>
+        <v>570519</v>
       </c>
       <c r="R9" t="n">
-        <v>6962474</v>
+        <v>6962421</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1458,7 @@
         <v>111785262</v>
       </c>
       <c r="B10" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,37 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111785277</v>
+        <v>111785263</v>
       </c>
       <c r="B11" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570624</v>
+        <v>570558</v>
       </c>
       <c r="R11" t="n">
-        <v>6962449</v>
+        <v>6962347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111785293</v>
+        <v>111785274</v>
       </c>
       <c r="B12" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1660,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570511</v>
+        <v>570728</v>
       </c>
       <c r="R12" t="n">
-        <v>6962472</v>
+        <v>6962307</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,12 +1749,7 @@
         <v>111785275</v>
       </c>
       <c r="B13" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,15 +1843,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111785274</v>
+        <v>111785276</v>
       </c>
       <c r="B14" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570729</v>
+        <v>570638</v>
       </c>
       <c r="R14" t="n">
-        <v>6962307</v>
+        <v>6962383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,37 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111785289</v>
+        <v>111785277</v>
       </c>
       <c r="B15" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570490</v>
+        <v>570624</v>
       </c>
       <c r="R15" t="n">
-        <v>6962361</v>
+        <v>6962449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111785283</v>
+        <v>111785267</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570566</v>
+        <v>570490</v>
       </c>
       <c r="R16" t="n">
-        <v>6962422</v>
+        <v>6962361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,15 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111785263</v>
+        <v>111785268</v>
       </c>
       <c r="B17" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570558</v>
+        <v>570519</v>
       </c>
       <c r="R17" t="n">
-        <v>6962347</v>
+        <v>6962482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,15 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111785254</v>
+        <v>111785255</v>
       </c>
       <c r="B18" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570519</v>
+        <v>570786</v>
       </c>
       <c r="R18" t="n">
-        <v>6962421</v>
+        <v>6962212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,37 +2328,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111785268</v>
+        <v>111785258</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570519</v>
+        <v>570692</v>
       </c>
       <c r="R19" t="n">
-        <v>6962482</v>
+        <v>6962274</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,37 +2425,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111785290</v>
+        <v>111785259</v>
       </c>
       <c r="B20" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570657</v>
+        <v>570576</v>
       </c>
       <c r="R20" t="n">
-        <v>6962474</v>
+        <v>6962420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,37 +2522,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111785259</v>
+        <v>111785260</v>
       </c>
       <c r="B21" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570576</v>
+        <v>570609</v>
       </c>
       <c r="R21" t="n">
-        <v>6962421</v>
+        <v>6962314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,53 +2619,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111785294</v>
+        <v>111785282</v>
       </c>
       <c r="B22" t="n">
-        <v>89955</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Stensjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570698</v>
+        <v>570621</v>
       </c>
       <c r="R22" t="n">
-        <v>6962175</v>
+        <v>6962392</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,7 +2698,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2818,6 +2713,103 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111785283</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Stensjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570567</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962422</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23506-2025 artfynd.xlsx
+++ b/artfynd/A 23506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785288</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785289</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785290</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785291</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785294</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785274</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785276</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785267</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785268</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785255</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785258</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785259</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785260</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785282</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,8 +2920,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111785283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>